--- a/docs/SECS/SECS_GEM功能_Handler_20260903.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260903.xlsx
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E57" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F57" s="40" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F58" s="40" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="E59" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F59" s="40" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E66" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="E67" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F67" s="40" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot 動態綁定模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接，Lot+Pass/Fail 模式時 Bin 號改為 PASS 或 FAIL；無任何綁定時為零長度</t>
+          <t>自訂 ASCII 編碼。⚠ 形狀隨分選模式改變：Normal 模式為該站對應的 Bin 號(例 '3')，若該站同時是錯誤/溢出目標則附加 ',ERR'(僅為錯誤目標時為 'ERR')；By Lot+Bin 模式為 '&lt;批號&gt;:&lt;Bin 號&gt;' 以半角逗號串接；By Lot+Pass/Fail 模式為〈分類碼本身〉'1'=PASS、'2'=FAIL（無批號前綴）；無任何綁定時為零長度。〔20260904 更正：By Lot+Pass/Fail 模式的值原為 '&lt;批號&gt;:PASS' / '&lt;批號&gt;:FAIL'，依貴端 2026-09-03 裁定改為裸分類碼，批號另由 SVID 66040-66045 提供，避免同一欄位承載兩種資訊。本機內部另有分類碼 0=錯誤 Bin，但錯誤/溢出流道永不進入綁定表，故本欄不會出現 0。Normal 與 By Lot+Bin 兩模式不變〕⚠ 本欄不再帶批號後，該流道的批號只剩 66040-66045 一個來源，而該組 SVID 在 Lot End 時隨綁定表一併清空，貴端請於貨批進行中讀取</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr">

--- a/docs/SECS/SECS_GEM功能_Handler_20260903.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260903.xlsx
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Clean Out 受理</t>
+          <t>Clean Out 受理(不分來源，每次排空只送一筆):畫面 Clean Out 鍵、面板 CLEAN OUT 鍵、S2F41 CLEAN_OUT、MES0920 Loader Tray Empty 對話框選 Clean Out(觸控或面板鍵皆可)、以及 AMR 模式下 Loader 進料源乾且叫車視窗逾時的自動進入。〔20260908 變更〕後兩者(對話框、AMR 自動)先前完全不發，host 只能由 CEID 27 的狀態文字推論；同版並移除「面板鍵在警報畫面上選取按鈕即發射」那一筆(選取後操作員仍可改選 RETRY，那筆會對應不到任何排空)，改為一律在真正進入 Clean Out 的瞬間發射。與 HT-90XX 同義:該機所有進入點亦共用同一發射點(TfMain::CleanOut)。</t>
         </is>
       </c>
     </row>
